--- a/it_forms/027_feature_details_form--it_forms.xlsx
+++ b/it_forms/027_feature_details_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'desktop',_'value':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Desktop', 'value': 'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'laptop',_'value':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Laptop', 'value': 'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'mobile',_'value':_'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Mobile', 'value': 'mobile'}</t>
+          <t>mobile</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'it',_'value':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'IT', 'value': 'it'}</t>
+          <t>it</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'operations',_'value':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Operations', 'value': 'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Marketing', 'value': 'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'sales',_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Sales', 'value': 'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'new',_'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'New', 'value': 'new'}</t>
+          <t>new</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Approved', 'value': 'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'rejected',_'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Rejected', 'value': 'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'archived',_'value':_'archived'}</t>
+          <t>archived</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'Archived', 'value': 'archived'}</t>
+          <t>archived</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'High', 'value': 'high'}</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Medium', 'value': 'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Low', 'value': 'low'}</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'bug',_'value':_'bug'}</t>
+          <t>bug</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Bug', 'value': 'bug'}</t>
+          <t>bug</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'new_feature',_'value':_'new_feature'}</t>
+          <t>new_feature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'New Feature', 'value': 'new_feature'}</t>
+          <t>new feature</t>
         </is>
       </c>
     </row>
